--- a/output/configurable/merged_dataset.xlsx
+++ b/output/configurable/merged_dataset.xlsx
@@ -463,17 +463,17 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>eu_noneu</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>short_long_term</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>mobility_record_count</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>eu_noneu</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>short_long_term</t>
         </is>
       </c>
     </row>
@@ -559,18 +559,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -612,18 +612,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -794,18 +794,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -1191,18 +1191,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -1330,18 +1330,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -1383,18 +1383,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -1522,18 +1522,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -1618,18 +1618,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="27">
@@ -1929,18 +1929,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="34">
@@ -2111,18 +2111,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
         <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="38">
@@ -2422,18 +2422,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
         <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="45">
@@ -2475,18 +2475,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
         <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="46">
@@ -2528,18 +2528,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="47">
@@ -2581,18 +2581,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
         <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="48">
@@ -2892,18 +2892,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
         <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="55">
@@ -3246,18 +3246,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I62" t="n">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
         <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="63">
@@ -3342,18 +3342,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I64" t="n">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
         <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="65">
@@ -3481,18 +3481,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I67" t="n">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
         <v>1</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="68">
@@ -3620,18 +3620,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I70" t="n">
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
         <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="71">
@@ -3716,18 +3716,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
         <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="73">
@@ -3769,18 +3769,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I73" t="n">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
         <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="74">
@@ -4037,18 +4037,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I79" t="n">
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
         <v>1</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="80">
@@ -4133,18 +4133,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I81" t="n">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
         <v>1</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="82">
@@ -4358,18 +4358,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I86" t="n">
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
         <v>1</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="87">
@@ -4626,18 +4626,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I92" t="n">
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
         <v>1</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="93">
@@ -4679,18 +4679,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I93" t="n">
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
         <v>1</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="94">
@@ -4732,18 +4732,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I94" t="n">
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
         <v>1</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="95">
@@ -5129,18 +5129,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I103" t="n">
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
         <v>1</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="104">
@@ -5397,18 +5397,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I109" t="n">
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
         <v>1</v>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="110">
@@ -5493,18 +5493,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I111" t="n">
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
         <v>1</v>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="112">
@@ -5589,18 +5589,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I113" t="n">
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
         <v>1</v>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="114">
@@ -5771,18 +5771,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I117" t="n">
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
         <v>1</v>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="118">
@@ -5824,18 +5824,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I118" t="n">
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
         <v>1</v>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="119">
@@ -6092,18 +6092,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I124" t="n">
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
         <v>1</v>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="125">
@@ -6145,18 +6145,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I125" t="n">
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
         <v>1</v>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="126">
@@ -6413,18 +6413,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I131" t="n">
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
         <v>1</v>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="132">
@@ -6552,18 +6552,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I134" t="n">
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
         <v>1</v>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="135">
@@ -6777,18 +6777,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I139" t="n">
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
         <v>1</v>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="140">
@@ -6830,18 +6830,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I140" t="n">
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
         <v>1</v>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="141">
@@ -6969,18 +6969,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I143" t="n">
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
         <v>1</v>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="144">
@@ -7065,18 +7065,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I145" t="n">
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
         <v>1</v>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="146">
@@ -7247,18 +7247,18 @@
           <t>graduates_2022.xlsx</t>
         </is>
       </c>
-      <c r="I149" t="n">
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
         <v>1</v>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="150">
@@ -7429,18 +7429,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I153" t="n">
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
         <v>2</v>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="154">
@@ -7525,18 +7525,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I155" t="n">
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
         <v>2</v>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="156">
@@ -7664,18 +7664,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I158" t="n">
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
         <v>1</v>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="159">
@@ -7975,18 +7975,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I165" t="n">
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
         <v>1</v>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="166">
@@ -8114,18 +8114,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I168" t="n">
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
         <v>1</v>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="169">
@@ -8210,18 +8210,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I170" t="n">
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
         <v>1</v>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="171">
@@ -8435,18 +8435,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I175" t="n">
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
         <v>1</v>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="176">
@@ -8531,18 +8531,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I177" t="n">
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
         <v>1</v>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="178">
@@ -8756,18 +8756,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I182" t="n">
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
         <v>2</v>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="183">
@@ -8981,18 +8981,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I187" t="n">
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
         <v>2</v>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="188">
@@ -9206,18 +9206,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I192" t="n">
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
         <v>1</v>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="193">
@@ -9345,18 +9345,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I195" t="n">
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
         <v>2</v>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="196">
@@ -9484,18 +9484,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I198" t="n">
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K198" t="n">
         <v>1</v>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="199">
@@ -9795,18 +9795,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I205" t="n">
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K205" t="n">
         <v>1</v>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="206">
@@ -9848,18 +9848,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I206" t="n">
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
         <v>1</v>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="207">
@@ -9987,18 +9987,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I209" t="n">
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
         <v>1</v>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="210">
@@ -10083,18 +10083,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I211" t="n">
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K211" t="n">
         <v>1</v>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="212">
@@ -10222,18 +10222,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I214" t="n">
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K214" t="n">
         <v>1</v>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="215">
@@ -10748,18 +10748,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I226" t="n">
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
         <v>2</v>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="227">
@@ -10801,18 +10801,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I227" t="n">
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
         <v>1</v>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="228">
@@ -10854,18 +10854,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I228" t="n">
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
         <v>2</v>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="229">
@@ -11079,18 +11079,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I233" t="n">
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K233" t="n">
         <v>1</v>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="234">
@@ -11304,18 +11304,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I238" t="n">
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K238" t="n">
         <v>2</v>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="239">
@@ -11357,18 +11357,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I239" t="n">
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K239" t="n">
         <v>2</v>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="240">
@@ -11410,18 +11410,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I240" t="n">
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K240" t="n">
         <v>1</v>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="241">
@@ -11592,18 +11592,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I244" t="n">
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K244" t="n">
         <v>2</v>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="245">
@@ -11817,18 +11817,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I249" t="n">
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
         <v>1</v>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="250">
@@ -11956,18 +11956,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I252" t="n">
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
         <v>2</v>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="253">
@@ -12181,18 +12181,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I257" t="n">
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
         <v>1</v>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="258">
@@ -12234,18 +12234,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I258" t="n">
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K258" t="n">
         <v>1</v>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="259">
@@ -12416,18 +12416,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I262" t="n">
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
         <v>1</v>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="263">
@@ -12469,18 +12469,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I263" t="n">
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
         <v>2</v>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="264">
@@ -12608,18 +12608,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I266" t="n">
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K266" t="n">
         <v>1</v>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="267">
@@ -12962,18 +12962,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I274" t="n">
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K274" t="n">
         <v>1</v>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="275">
@@ -13101,18 +13101,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I277" t="n">
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K277" t="n">
         <v>1</v>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="278">
@@ -13154,18 +13154,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I278" t="n">
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K278" t="n">
         <v>1</v>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="279">
@@ -13336,18 +13336,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I282" t="n">
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K282" t="n">
         <v>1</v>
-      </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="283">
@@ -13432,18 +13432,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I284" t="n">
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K284" t="n">
         <v>1</v>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="285">
@@ -13657,18 +13657,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I289" t="n">
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K289" t="n">
         <v>1</v>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="290">
@@ -14054,18 +14054,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I298" t="n">
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K298" t="n">
         <v>1</v>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="299">
@@ -14107,18 +14107,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I299" t="n">
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K299" t="n">
         <v>1</v>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="300">
@@ -14203,18 +14203,18 @@
           <t>graduates_2023.xlsx</t>
         </is>
       </c>
-      <c r="I301" t="n">
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K301" t="n">
         <v>1</v>
-      </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="302">
@@ -14471,18 +14471,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I307" t="n">
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K307" t="n">
         <v>1</v>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="308">
@@ -14610,18 +14610,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I310" t="n">
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K310" t="n">
         <v>1</v>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="311">
@@ -14706,18 +14706,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I312" t="n">
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K312" t="n">
         <v>1</v>
-      </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="313">
@@ -14759,18 +14759,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I313" t="n">
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K313" t="n">
         <v>1</v>
-      </c>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="314">
@@ -15027,18 +15027,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I319" t="n">
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K319" t="n">
         <v>1</v>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="320">
@@ -15123,18 +15123,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I321" t="n">
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K321" t="n">
         <v>1</v>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="322">
@@ -15305,18 +15305,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I325" t="n">
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K325" t="n">
         <v>1</v>
-      </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="326">
@@ -15444,18 +15444,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I328" t="n">
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K328" t="n">
         <v>1</v>
-      </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="329">
@@ -15712,18 +15712,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I334" t="n">
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K334" t="n">
         <v>1</v>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="335">
@@ -15808,18 +15808,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I336" t="n">
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K336" t="n">
         <v>1</v>
-      </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="337">
@@ -16076,18 +16076,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I342" t="n">
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K342" t="n">
         <v>1</v>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="343">
@@ -16129,18 +16129,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I343" t="n">
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K343" t="n">
         <v>1</v>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="344">
@@ -16268,18 +16268,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I346" t="n">
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K346" t="n">
         <v>2</v>
-      </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="347">
@@ -16364,18 +16364,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I348" t="n">
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K348" t="n">
         <v>1</v>
-      </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="349">
@@ -16632,18 +16632,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I354" t="n">
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K354" t="n">
         <v>2</v>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="355">
@@ -16771,18 +16771,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I357" t="n">
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K357" t="n">
         <v>1</v>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="358">
@@ -16953,18 +16953,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I361" t="n">
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K361" t="n">
         <v>2</v>
-      </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K361" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="362">
@@ -17178,18 +17178,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I366" t="n">
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K366" t="n">
         <v>1</v>
-      </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="367">
@@ -17317,18 +17317,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I369" t="n">
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K369" t="n">
         <v>1</v>
-      </c>
-      <c r="J369" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="370">
@@ -17370,18 +17370,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I370" t="n">
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K370" t="n">
         <v>1</v>
-      </c>
-      <c r="J370" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="371">
@@ -17724,18 +17724,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I378" t="n">
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K378" t="n">
         <v>1</v>
-      </c>
-      <c r="J378" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K378" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="379">
@@ -17820,18 +17820,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I380" t="n">
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K380" t="n">
         <v>1</v>
-      </c>
-      <c r="J380" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K380" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="381">
@@ -17959,18 +17959,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I383" t="n">
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K383" t="n">
         <v>1</v>
-      </c>
-      <c r="J383" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K383" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="384">
@@ -18012,18 +18012,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I384" t="n">
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K384" t="n">
         <v>2</v>
-      </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K384" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="385">
@@ -18280,18 +18280,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I390" t="n">
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K390" t="n">
         <v>1</v>
-      </c>
-      <c r="J390" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K390" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="391">
@@ -18376,18 +18376,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I392" t="n">
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K392" t="n">
         <v>1</v>
-      </c>
-      <c r="J392" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K392" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="393">
@@ -18730,18 +18730,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I400" t="n">
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K400" t="n">
         <v>1</v>
-      </c>
-      <c r="J400" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K400" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="401">
@@ -18912,18 +18912,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I404" t="n">
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K404" t="n">
         <v>1</v>
-      </c>
-      <c r="J404" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K404" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="405">
@@ -19051,18 +19051,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I407" t="n">
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K407" t="n">
         <v>1</v>
-      </c>
-      <c r="J407" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K407" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="408">
@@ -19190,18 +19190,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I410" t="n">
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K410" t="n">
         <v>1</v>
-      </c>
-      <c r="J410" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K410" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="411">
@@ -19372,18 +19372,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I414" t="n">
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K414" t="n">
         <v>2</v>
-      </c>
-      <c r="J414" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K414" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="415">
@@ -19554,18 +19554,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I418" t="n">
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K418" t="n">
         <v>1</v>
-      </c>
-      <c r="J418" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K418" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="419">
@@ -19693,18 +19693,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I421" t="n">
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K421" t="n">
         <v>1</v>
-      </c>
-      <c r="J421" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="422">
@@ -19918,18 +19918,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I426" t="n">
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K426" t="n">
         <v>1</v>
-      </c>
-      <c r="J426" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K426" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="427">
@@ -19971,18 +19971,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I427" t="n">
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K427" t="n">
         <v>1</v>
-      </c>
-      <c r="J427" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K427" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="428">
@@ -20024,18 +20024,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I428" t="n">
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K428" t="n">
         <v>1</v>
-      </c>
-      <c r="J428" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K428" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="429">
@@ -20292,18 +20292,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I434" t="n">
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K434" t="n">
         <v>1</v>
-      </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K434" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="435">
@@ -20517,18 +20517,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I439" t="n">
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K439" t="n">
         <v>1</v>
-      </c>
-      <c r="J439" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K439" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="440">
@@ -20570,18 +20570,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I440" t="n">
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K440" t="n">
         <v>1</v>
-      </c>
-      <c r="J440" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K440" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="441">
@@ -20752,18 +20752,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I444" t="n">
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K444" t="n">
         <v>2</v>
-      </c>
-      <c r="J444" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K444" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="445">
@@ -20934,18 +20934,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I448" t="n">
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K448" t="n">
         <v>1</v>
-      </c>
-      <c r="J448" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K448" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="449">
@@ -21030,18 +21030,18 @@
           <t>graduates_2024.xlsx</t>
         </is>
       </c>
-      <c r="I450" t="n">
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K450" t="n">
         <v>2</v>
-      </c>
-      <c r="J450" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K450" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="451">
@@ -21169,18 +21169,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I453" t="n">
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K453" t="n">
         <v>1</v>
-      </c>
-      <c r="J453" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K453" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="454">
@@ -21222,18 +21222,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I454" t="n">
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K454" t="n">
         <v>1</v>
-      </c>
-      <c r="J454" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K454" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="455">
@@ -21318,18 +21318,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I456" t="n">
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K456" t="n">
         <v>1</v>
-      </c>
-      <c r="J456" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K456" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="457">
@@ -21672,18 +21672,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I464" t="n">
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K464" t="n">
         <v>1</v>
-      </c>
-      <c r="J464" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K464" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="465">
@@ -21983,18 +21983,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I471" t="n">
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K471" t="n">
         <v>1</v>
-      </c>
-      <c r="J471" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K471" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="472">
@@ -22079,18 +22079,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I473" t="n">
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K473" t="n">
         <v>1</v>
-      </c>
-      <c r="J473" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K473" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="474">
@@ -22132,18 +22132,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I474" t="n">
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K474" t="n">
         <v>1</v>
-      </c>
-      <c r="J474" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K474" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="475">
@@ -22185,18 +22185,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I475" t="n">
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K475" t="n">
         <v>1</v>
-      </c>
-      <c r="J475" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K475" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="476">
@@ -22410,18 +22410,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I480" t="n">
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K480" t="n">
         <v>1</v>
-      </c>
-      <c r="J480" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K480" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="481">
@@ -22807,18 +22807,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I489" t="n">
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K489" t="n">
         <v>1</v>
-      </c>
-      <c r="J489" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K489" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="490">
@@ -22903,18 +22903,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I491" t="n">
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K491" t="n">
         <v>1</v>
-      </c>
-      <c r="J491" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K491" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="492">
@@ -23085,18 +23085,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I495" t="n">
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K495" t="n">
         <v>1</v>
-      </c>
-      <c r="J495" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K495" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="496">
@@ -23267,18 +23267,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I499" t="n">
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K499" t="n">
         <v>1</v>
-      </c>
-      <c r="J499" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K499" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="500">
@@ -23320,18 +23320,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I500" t="n">
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K500" t="n">
         <v>1</v>
-      </c>
-      <c r="J500" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K500" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="501">
@@ -23416,18 +23416,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I502" t="n">
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K502" t="n">
         <v>1</v>
-      </c>
-      <c r="J502" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K502" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="503">
@@ -23856,18 +23856,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I512" t="n">
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K512" t="n">
         <v>1</v>
-      </c>
-      <c r="J512" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K512" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="513">
@@ -23952,18 +23952,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I514" t="n">
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K514" t="n">
         <v>1</v>
-      </c>
-      <c r="J514" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K514" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="515">
@@ -24091,18 +24091,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I517" t="n">
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K517" t="n">
         <v>1</v>
-      </c>
-      <c r="J517" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K517" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="518">
@@ -24316,18 +24316,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I522" t="n">
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K522" t="n">
         <v>1</v>
-      </c>
-      <c r="J522" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K522" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="523">
@@ -24412,18 +24412,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I524" t="n">
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K524" t="n">
         <v>1</v>
-      </c>
-      <c r="J524" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K524" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="525">
@@ -24465,18 +24465,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I525" t="n">
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K525" t="n">
         <v>1</v>
-      </c>
-      <c r="J525" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K525" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="526">
@@ -24690,18 +24690,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I530" t="n">
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K530" t="n">
         <v>1</v>
-      </c>
-      <c r="J530" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K530" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="531">
@@ -24958,18 +24958,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I536" t="n">
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K536" t="n">
         <v>1</v>
-      </c>
-      <c r="J536" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K536" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="537">
@@ -25054,18 +25054,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I538" t="n">
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K538" t="n">
         <v>1</v>
-      </c>
-      <c r="J538" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K538" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="539">
@@ -25193,18 +25193,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I541" t="n">
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K541" t="n">
         <v>1</v>
-      </c>
-      <c r="J541" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K541" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="542">
@@ -25332,18 +25332,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I544" t="n">
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K544" t="n">
         <v>2</v>
-      </c>
-      <c r="J544" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K544" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="545">
@@ -25385,18 +25385,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I545" t="n">
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K545" t="n">
         <v>1</v>
-      </c>
-      <c r="J545" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K545" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="546">
@@ -25653,18 +25653,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I551" t="n">
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K551" t="n">
         <v>2</v>
-      </c>
-      <c r="J551" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K551" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="552">
@@ -25878,18 +25878,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I556" t="n">
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K556" t="n">
         <v>2</v>
-      </c>
-      <c r="J556" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K556" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="557">
@@ -26103,18 +26103,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I561" t="n">
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K561" t="n">
         <v>1</v>
-      </c>
-      <c r="J561" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K561" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="562">
@@ -26285,18 +26285,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I565" t="n">
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K565" t="n">
         <v>1</v>
-      </c>
-      <c r="J565" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K565" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="566">
@@ -26510,18 +26510,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I570" t="n">
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K570" t="n">
         <v>1</v>
-      </c>
-      <c r="J570" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K570" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="571">
@@ -26563,18 +26563,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I571" t="n">
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K571" t="n">
         <v>1</v>
-      </c>
-      <c r="J571" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K571" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="572">
@@ -26788,18 +26788,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I576" t="n">
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K576" t="n">
         <v>2</v>
-      </c>
-      <c r="J576" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K576" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="577">
@@ -26884,18 +26884,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I578" t="n">
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K578" t="n">
         <v>1</v>
-      </c>
-      <c r="J578" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K578" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="579">
@@ -26937,18 +26937,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I579" t="n">
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K579" t="n">
         <v>1</v>
-      </c>
-      <c r="J579" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K579" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="580">
@@ -27162,18 +27162,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I584" t="n">
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K584" t="n">
         <v>2</v>
-      </c>
-      <c r="J584" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K584" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="585">
@@ -27215,18 +27215,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I585" t="n">
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K585" t="n">
         <v>1</v>
-      </c>
-      <c r="J585" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K585" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="586">
@@ -27268,18 +27268,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I586" t="n">
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K586" t="n">
         <v>1</v>
-      </c>
-      <c r="J586" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K586" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="587">
@@ -27579,18 +27579,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I593" t="n">
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K593" t="n">
         <v>1</v>
-      </c>
-      <c r="J593" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K593" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="594">
@@ -27890,18 +27890,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I600" t="n">
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K600" t="n">
         <v>1</v>
-      </c>
-      <c r="J600" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K600" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="601">
@@ -27943,18 +27943,18 @@
           <t>graduates_2025.xlsx</t>
         </is>
       </c>
-      <c r="I601" t="n">
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K601" t="n">
         <v>1</v>
-      </c>
-      <c r="J601" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K601" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="602">
@@ -28039,18 +28039,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I603" t="n">
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K603" t="n">
         <v>1</v>
-      </c>
-      <c r="J603" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K603" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="604">
@@ -28092,18 +28092,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I604" t="n">
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K604" t="n">
         <v>1</v>
-      </c>
-      <c r="J604" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K604" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="605">
@@ -28360,18 +28360,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I610" t="n">
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K610" t="n">
         <v>1</v>
-      </c>
-      <c r="J610" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K610" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="611">
@@ -28499,18 +28499,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I613" t="n">
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K613" t="n">
         <v>1</v>
-      </c>
-      <c r="J613" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K613" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="614">
@@ -28724,18 +28724,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I618" t="n">
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K618" t="n">
         <v>1</v>
-      </c>
-      <c r="J618" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K618" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="619">
@@ -28820,18 +28820,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I620" t="n">
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K620" t="n">
         <v>1</v>
-      </c>
-      <c r="J620" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K620" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="621">
@@ -29174,18 +29174,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I628" t="n">
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K628" t="n">
         <v>1</v>
-      </c>
-      <c r="J628" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K628" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="629">
@@ -29313,18 +29313,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I631" t="n">
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K631" t="n">
         <v>1</v>
-      </c>
-      <c r="J631" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K631" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="632">
@@ -29409,18 +29409,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I633" t="n">
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K633" t="n">
         <v>2</v>
-      </c>
-      <c r="J633" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K633" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="634">
@@ -29505,18 +29505,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I635" t="n">
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K635" t="n">
         <v>1</v>
-      </c>
-      <c r="J635" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K635" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="636">
@@ -29601,18 +29601,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I637" t="n">
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K637" t="n">
         <v>1</v>
-      </c>
-      <c r="J637" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K637" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="638">
@@ -29826,18 +29826,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I642" t="n">
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K642" t="n">
         <v>1</v>
-      </c>
-      <c r="J642" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K642" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="643">
@@ -30051,18 +30051,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I647" t="n">
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K647" t="n">
         <v>2</v>
-      </c>
-      <c r="J647" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K647" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="648">
@@ -30147,18 +30147,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I649" t="n">
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K649" t="n">
         <v>1</v>
-      </c>
-      <c r="J649" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K649" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="650">
@@ -30200,18 +30200,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I650" t="n">
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K650" t="n">
         <v>2</v>
-      </c>
-      <c r="J650" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K650" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="651">
@@ -30554,18 +30554,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I658" t="n">
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K658" t="n">
         <v>1</v>
-      </c>
-      <c r="J658" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K658" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="659">
@@ -30693,18 +30693,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I661" t="n">
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K661" t="n">
         <v>1</v>
-      </c>
-      <c r="J661" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K661" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="662">
@@ -30875,18 +30875,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I665" t="n">
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K665" t="n">
         <v>1</v>
-      </c>
-      <c r="J665" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K665" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="666">
@@ -31143,18 +31143,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I671" t="n">
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K671" t="n">
         <v>1</v>
-      </c>
-      <c r="J671" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K671" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="672">
@@ -31196,18 +31196,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I672" t="n">
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K672" t="n">
         <v>1</v>
-      </c>
-      <c r="J672" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K672" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="673">
@@ -31249,18 +31249,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I673" t="n">
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K673" t="n">
         <v>2</v>
-      </c>
-      <c r="J673" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K673" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="674">
@@ -31560,18 +31560,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I680" t="n">
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K680" t="n">
         <v>1</v>
-      </c>
-      <c r="J680" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K680" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="681">
@@ -31785,18 +31785,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I685" t="n">
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K685" t="n">
         <v>2</v>
-      </c>
-      <c r="J685" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K685" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="686">
@@ -31924,18 +31924,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I688" t="n">
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K688" t="n">
         <v>1</v>
-      </c>
-      <c r="J688" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K688" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="689">
@@ -32020,18 +32020,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I690" t="n">
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K690" t="n">
         <v>1</v>
-      </c>
-      <c r="J690" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K690" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="691">
@@ -32116,18 +32116,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I692" t="n">
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K692" t="n">
         <v>1</v>
-      </c>
-      <c r="J692" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K692" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="693">
@@ -32169,18 +32169,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I693" t="n">
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K693" t="n">
         <v>1</v>
-      </c>
-      <c r="J693" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K693" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="694">
@@ -32652,18 +32652,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I704" t="n">
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K704" t="n">
         <v>1</v>
-      </c>
-      <c r="J704" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K704" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="705">
@@ -32920,18 +32920,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I710" t="n">
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K710" t="n">
         <v>1</v>
-      </c>
-      <c r="J710" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K710" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="711">
@@ -32973,18 +32973,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I711" t="n">
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K711" t="n">
         <v>1</v>
-      </c>
-      <c r="J711" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K711" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="712">
@@ -33026,18 +33026,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I712" t="n">
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K712" t="n">
         <v>2</v>
-      </c>
-      <c r="J712" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K712" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="713">
@@ -33122,18 +33122,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I714" t="n">
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K714" t="n">
         <v>1</v>
-      </c>
-      <c r="J714" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K714" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="715">
@@ -33218,18 +33218,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I716" t="n">
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K716" t="n">
         <v>1</v>
-      </c>
-      <c r="J716" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K716" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="717">
@@ -33615,18 +33615,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I725" t="n">
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K725" t="n">
         <v>1</v>
-      </c>
-      <c r="J725" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K725" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="726">
@@ -33797,18 +33797,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I729" t="n">
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K729" t="n">
         <v>1</v>
-      </c>
-      <c r="J729" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K729" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="730">
@@ -33893,18 +33893,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I731" t="n">
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K731" t="n">
         <v>1</v>
-      </c>
-      <c r="J731" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K731" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="732">
@@ -34032,18 +34032,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I734" t="n">
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K734" t="n">
         <v>1</v>
-      </c>
-      <c r="J734" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K734" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="735">
@@ -34171,18 +34171,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I737" t="n">
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K737" t="n">
         <v>1</v>
-      </c>
-      <c r="J737" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K737" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="738">
@@ -34224,18 +34224,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I738" t="n">
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K738" t="n">
         <v>1</v>
-      </c>
-      <c r="J738" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K738" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="739">
@@ -34449,18 +34449,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I743" t="n">
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K743" t="n">
         <v>1</v>
-      </c>
-      <c r="J743" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K743" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
     <row r="744">
@@ -34760,18 +34760,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I750" t="n">
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="K750" t="n">
         <v>2</v>
-      </c>
-      <c r="J750" t="inlineStr">
-        <is>
-          <t>EU-27</t>
-        </is>
-      </c>
-      <c r="K750" t="inlineStr">
-        <is>
-          <t>Long-term</t>
-        </is>
       </c>
     </row>
     <row r="751">
@@ -34813,18 +34813,18 @@
           <t>graduates_2026.xlsx</t>
         </is>
       </c>
-      <c r="I751" t="n">
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>Non-EU</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="K751" t="n">
         <v>1</v>
-      </c>
-      <c r="J751" t="inlineStr">
-        <is>
-          <t>Non-EU</t>
-        </is>
-      </c>
-      <c r="K751" t="inlineStr">
-        <is>
-          <t>Short-term</t>
-        </is>
       </c>
     </row>
   </sheetData>
